--- a/resources/pet/pet_evolve.xlsx
+++ b/resources/pet/pet_evolve.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="7.75" customWidth="1" style="16" min="1" max="1"/>
@@ -2789,6 +2789,51 @@
       <c r="P45" s="34" t="n"/>
       <c r="Q45" s="34" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="29" t="n">
+        <v>10042</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>进化到20999九尾天狐·终焉，消耗10050×3、10051×2</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>3067</v>
+      </c>
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="31" t="n"/>
+      <c r="F46" s="33" t="n">
+        <v>20999</v>
+      </c>
+      <c r="G46" s="32" t="n"/>
+      <c r="H46" s="35" t="inlineStr">
+        <is>
+          <t>10050</t>
+        </is>
+      </c>
+      <c r="I46" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" s="34" t="inlineStr">
+        <is>
+          <t>10051</t>
+        </is>
+      </c>
+      <c r="K46" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="34" t="n"/>
+      <c r="M46" s="34" t="n"/>
+      <c r="N46" s="34" t="n"/>
+      <c r="O46" s="34" t="n"/>
+      <c r="P46" s="34" t="n"/>
+      <c r="Q46" s="34" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 C1:C4">
     <cfRule type="duplicateValues" priority="1977" dxfId="0"/>

--- a/resources/pet/pet_evolve.xlsx
+++ b/resources/pet/pet_evolve.xlsx
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="7.75" customWidth="1" style="16" min="1" max="1"/>
@@ -2751,88 +2751,35 @@
       <c r="A45" s="29" t="n">
         <v>10041</v>
       </c>
-      <c r="C45" s="33" t="n"/>
+      <c r="C45" s="33" t="n">
+        <v>510001</v>
+      </c>
       <c r="D45" s="32" t="n"/>
-      <c r="E45" s="31" t="n"/>
+      <c r="E45" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="F45" s="33" t="n">
-        <v>20999</v>
-      </c>
-      <c r="G45" s="32" t="inlineStr">
-        <is>
-          <t>九尾天狐·终焉</t>
-        </is>
-      </c>
+        <v>510002</v>
+      </c>
+      <c r="G45" s="32" t="n"/>
       <c r="H45" s="35" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>510001</t>
         </is>
       </c>
       <c r="I45" s="35" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" s="34" t="inlineStr">
-        <is>
-          <t>10051</t>
-        </is>
-      </c>
-      <c r="K45" s="34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" s="34" t="n"/>
+      <c r="K45" s="34" t="n"/>
       <c r="L45" s="34" t="n"/>
       <c r="M45" s="34" t="n"/>
       <c r="N45" s="34" t="n"/>
       <c r="O45" s="34" t="n"/>
       <c r="P45" s="34" t="n"/>
       <c r="Q45" s="34" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="n">
-        <v>10042</v>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>进化到20999九尾天狐·终焉，消耗10050×3、10051×2</t>
-        </is>
-      </c>
-      <c r="C46" s="33" t="n">
-        <v>3067</v>
-      </c>
-      <c r="D46" s="32" t="n"/>
-      <c r="E46" s="31" t="n"/>
-      <c r="F46" s="33" t="n">
-        <v>20999</v>
-      </c>
-      <c r="G46" s="32" t="n"/>
-      <c r="H46" s="35" t="inlineStr">
-        <is>
-          <t>10050</t>
-        </is>
-      </c>
-      <c r="I46" s="35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" s="34" t="inlineStr">
-        <is>
-          <t>10051</t>
-        </is>
-      </c>
-      <c r="K46" s="34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L46" s="34" t="n"/>
-      <c r="M46" s="34" t="n"/>
-      <c r="N46" s="34" t="n"/>
-      <c r="O46" s="34" t="n"/>
-      <c r="P46" s="34" t="n"/>
-      <c r="Q46" s="34" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 C1:C4">
